--- a/dados/excel/genero_por_escolaridade.xlsx
+++ b/dados/excel/genero_por_escolaridade.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026 19:18</t>
+          <t>10/10/2026 14:55</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
         <v>15</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>3232.282437417655</v>
+        <v>3239.608645833333</v>
       </c>
     </row>
     <row r="3">
@@ -808,7 +808,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="15" t="n">
-        <v>4890.813663911846</v>
+        <v>4897.920493150685</v>
       </c>
     </row>
     <row r="4">
@@ -826,7 +826,7 @@
         <v>55</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>3655.850968978738</v>
+        <v>3666.506639118457</v>
       </c>
     </row>
     <row r="5">
@@ -844,7 +844,7 @@
         <v>2</v>
       </c>
       <c r="D5" s="15" t="n">
-        <v>6422.762500000001</v>
+        <v>6436.1192</v>
       </c>
     </row>
     <row r="6">
@@ -862,7 +862,7 @@
         <v>70</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>5716.802977993712</v>
+        <v>5755.664380305603</v>
       </c>
     </row>
     <row r="7">
@@ -877,10 +877,10 @@
         </is>
       </c>
       <c r="C7" s="14" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D7" s="15" t="n">
-        <v>3851.671832615716</v>
+        <v>3868.750557522123</v>
       </c>
     </row>
     <row r="8">
@@ -898,7 +898,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>3155.423731778426</v>
+        <v>3166.941729106628</v>
       </c>
     </row>
     <row r="9">
@@ -913,10 +913,10 @@
         </is>
       </c>
       <c r="C9" s="14" t="n">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D9" s="15" t="n">
-        <v>4954.925888888889</v>
+        <v>4964.534844020797</v>
       </c>
     </row>
     <row r="10">
@@ -934,7 +934,7 @@
         <v>34</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>4008.903049289891</v>
+        <v>4032.189222497932</v>
       </c>
     </row>
     <row r="11">
@@ -952,7 +952,7 @@
         <v>20</v>
       </c>
       <c r="D11" s="15" t="n">
-        <v>7583.122842920354</v>
+        <v>7601.237302631579</v>
       </c>
     </row>
     <row r="12">
@@ -967,10 +967,10 @@
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>3728</v>
+        <v>3769</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>4103.596184119388</v>
+        <v>4125.062270205995</v>
       </c>
     </row>
     <row r="13">
@@ -985,10 +985,10 @@
         </is>
       </c>
       <c r="C13" s="14" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D13" s="15" t="n">
-        <v>5035.80749005425</v>
+        <v>5073.757917555082</v>
       </c>
     </row>
     <row r="14">
@@ -1003,10 +1003,10 @@
         </is>
       </c>
       <c r="C14" s="10" t="n">
-        <v>1597</v>
+        <v>1610</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>5881.653279580797</v>
+        <v>5901.882658493813</v>
       </c>
     </row>
     <row r="15">
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="C15" s="14" t="n">
-        <v>3886</v>
+        <v>3931</v>
       </c>
       <c r="D15" s="15" t="n">
-        <v>1631.819625193882</v>
+        <v>1639.598133846392</v>
       </c>
     </row>
     <row r="16">
@@ -1042,7 +1042,7 @@
         <v>44</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>2360.052655538695</v>
+        <v>2378.938963963964</v>
       </c>
     </row>
     <row r="17">
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="C17" s="14" t="n">
-        <v>960</v>
+        <v>974</v>
       </c>
       <c r="D17" s="15" t="n">
-        <v>2899.67851245283</v>
+        <v>2905.084359450427</v>
       </c>
     </row>
     <row r="18">
@@ -1075,10 +1075,10 @@
         </is>
       </c>
       <c r="C18" s="10" t="n">
-        <v>10444</v>
+        <v>10687</v>
       </c>
       <c r="D18" s="11" t="n">
-        <v>6247.210986807952</v>
+        <v>6273.949586329277</v>
       </c>
     </row>
     <row r="19">
@@ -1093,10 +1093,10 @@
         </is>
       </c>
       <c r="C19" s="14" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D19" s="15" t="n">
-        <v>8024.158480440337</v>
+        <v>8028.406695668987</v>
       </c>
     </row>
     <row r="20">
@@ -1111,10 +1111,10 @@
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>2210</v>
+        <v>2236</v>
       </c>
       <c r="D20" s="11" t="n">
-        <v>10878.74957097395</v>
+        <v>10919.83821982437</v>
       </c>
     </row>
     <row r="21">
@@ -1129,10 +1129,10 @@
         </is>
       </c>
       <c r="C21" s="14" t="n">
-        <v>2474</v>
+        <v>2478</v>
       </c>
       <c r="D21" s="15" t="n">
-        <v>10631.29923657958</v>
+        <v>10692.0785287543</v>
       </c>
     </row>
     <row r="22">
@@ -1150,7 +1150,7 @@
         <v>47</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>9877.117733897509</v>
+        <v>9931.488874478926</v>
       </c>
     </row>
     <row r="23">
@@ -1168,7 +1168,7 @@
         <v>331</v>
       </c>
       <c r="D23" s="15" t="n">
-        <v>16321.12117233496</v>
+        <v>16389.2083712676</v>
       </c>
     </row>
     <row r="24">
@@ -1186,7 +1186,7 @@
         <v>100</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>13599.40429044054</v>
+        <v>13696.97279883382</v>
       </c>
     </row>
     <row r="25">
@@ -1204,7 +1204,7 @@
         <v>2</v>
       </c>
       <c r="D25" s="15" t="n">
-        <v>25492.18812080537</v>
+        <v>25644.53973509934</v>
       </c>
     </row>
     <row r="26">
@@ -1222,7 +1222,7 @@
         <v>43</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>15326.81516923077</v>
+        <v>15395.63915845337</v>
       </c>
     </row>
     <row r="27">
@@ -1240,7 +1240,7 @@
         <v>21</v>
       </c>
       <c r="D27" s="15" t="n">
-        <v>13902.32280127693</v>
+        <v>13973.19642969984</v>
       </c>
     </row>
     <row r="28">
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="C28" s="10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>16640.27856870229</v>
+        <v>16764.28599437148</v>
       </c>
     </row>
   </sheetData>
